--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D69C7D3-5DD2-456B-95F4-04539AC3C5CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD5070F3-9D25-411D-A29C-70272244D477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5705"/>
+  <dimension ref="A1:E5707"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -97442,6 +97442,40 @@
         <v>637</v>
       </c>
     </row>
+    <row r="5706" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5706">
+        <v>620426</v>
+      </c>
+      <c r="B5706">
+        <v>20261027</v>
+      </c>
+      <c r="C5706" s="1">
+        <v>9241</v>
+      </c>
+      <c r="D5706" s="1">
+        <v>6818</v>
+      </c>
+      <c r="E5706" s="1">
+        <v>4768</v>
+      </c>
+    </row>
+    <row r="5707" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5707">
+        <v>620526</v>
+      </c>
+      <c r="B5707">
+        <v>20261028</v>
+      </c>
+      <c r="C5707" s="1">
+        <v>7986</v>
+      </c>
+      <c r="D5707" s="1">
+        <v>3692</v>
+      </c>
+      <c r="E5707" s="1">
+        <v>4564</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
